--- a/excel/6. Temporal Ranks Comparison & Borda.xlsx
+++ b/excel/6. Temporal Ranks Comparison & Borda.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LAPTOP 35\Desktop\PhD\2. Fuzzy (1-IJMEMS)\2. Code\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LAPTOP 35\Desktop\PhD\2. Fuzzy (1-IJMEMS)\git\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6C3E0D8-A984-4C1B-9864-00D9F7C6B3AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFD59B0E-7F95-444B-934A-E549A49128FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{57971DE3-9D18-4B35-A82F-75B938ED0AF1}"/>
   </bookViews>
@@ -285,13 +285,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="8"/>
       <color theme="1"/>
       <name val="Segoe UI"/>
@@ -331,6 +324,14 @@
       <color theme="1"/>
       <name val="Segoe UI"/>
       <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -379,45 +380,40 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -608,10 +604,10 @@
                   <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>14</c:v>
+                  <c:v>16</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>7</c:v>
+                  <c:v>6</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>3</c:v>
@@ -623,7 +619,7 @@
                   <c:v>13</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>15</c:v>
+                  <c:v>14</c:v>
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>4</c:v>
@@ -632,7 +628,7 @@
                   <c:v>2</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>16</c:v>
+                  <c:v>15</c:v>
                 </c:pt>
                 <c:pt idx="11">
                   <c:v>5</c:v>
@@ -641,7 +637,7 @@
                   <c:v>10</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>6</c:v>
+                  <c:v>7</c:v>
                 </c:pt>
                 <c:pt idx="14">
                   <c:v>12</c:v>
@@ -764,7 +760,7 @@
                   <c:v>11</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>14</c:v>
+                  <c:v>15</c:v>
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>2</c:v>
@@ -782,10 +778,10 @@
                   <c:v>10</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>15</c:v>
+                  <c:v>13</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>13</c:v>
+                  <c:v>14</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -884,7 +880,7 @@
                   <c:v>4</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>15</c:v>
+                  <c:v>16</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>8</c:v>
@@ -893,7 +889,7 @@
                   <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>14</c:v>
+                  <c:v>15</c:v>
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>9</c:v>
@@ -908,7 +904,7 @@
                   <c:v>2</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>16</c:v>
+                  <c:v>14</c:v>
                 </c:pt>
                 <c:pt idx="11">
                   <c:v>5</c:v>
@@ -1016,16 +1012,16 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="16"/>
                 <c:pt idx="0">
-                  <c:v>14</c:v>
+                  <c:v>10</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>3</c:v>
+                  <c:v>4</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>11</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>13</c:v>
+                  <c:v>14</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>2</c:v>
@@ -1040,7 +1036,7 @@
                   <c:v>15</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>10</c:v>
+                  <c:v>13</c:v>
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>1</c:v>
@@ -1058,7 +1054,7 @@
                   <c:v>6</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>4</c:v>
+                  <c:v>3</c:v>
                 </c:pt>
                 <c:pt idx="15">
                   <c:v>16</c:v>
@@ -1154,7 +1150,7 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="16"/>
                 <c:pt idx="0">
-                  <c:v>6</c:v>
+                  <c:v>7</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>3</c:v>
@@ -1163,7 +1159,7 @@
                   <c:v>16</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>11</c:v>
+                  <c:v>10</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>2</c:v>
@@ -1175,10 +1171,10 @@
                   <c:v>9</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>15</c:v>
+                  <c:v>14</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>10</c:v>
+                  <c:v>12</c:v>
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>4</c:v>
@@ -1190,16 +1186,16 @@
                   <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>7</c:v>
+                  <c:v>6</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>12</c:v>
+                  <c:v>13</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>14</c:v>
+                  <c:v>15</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>13</c:v>
+                  <c:v>11</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1298,7 +1294,7 @@
                   <c:v>3</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>15</c:v>
+                  <c:v>14</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>8</c:v>
@@ -1307,13 +1303,13 @@
                   <c:v>9</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>13</c:v>
+                  <c:v>15</c:v>
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>11</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>14</c:v>
+                  <c:v>12</c:v>
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>1</c:v>
@@ -1334,7 +1330,7 @@
                   <c:v>4</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>12</c:v>
+                  <c:v>13</c:v>
                 </c:pt>
                 <c:pt idx="15">
                   <c:v>16</c:v>
@@ -1447,7 +1443,7 @@
                   <c:v>5</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>9</c:v>
+                  <c:v>10</c:v>
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>16</c:v>
@@ -1468,13 +1464,13 @@
                   <c:v>13</c:v>
                 </c:pt>
                 <c:pt idx="12">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="13">
                   <c:v>12</c:v>
                 </c:pt>
-                <c:pt idx="13">
-                  <c:v>11</c:v>
-                </c:pt>
                 <c:pt idx="14">
-                  <c:v>10</c:v>
+                  <c:v>9</c:v>
                 </c:pt>
                 <c:pt idx="15">
                   <c:v>7</c:v>
@@ -2622,40 +2618,41 @@
       <c r="H1" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="J1" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="K1" s="3"/>
+      <c r="K1" s="8"/>
     </row>
     <row r="2" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="B2" s="11" t="s">
+      <c r="B2" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="C2" s="11" t="s">
+      <c r="C2" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="D2" s="11" t="s">
+      <c r="D2" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="E2" s="11" t="s">
+      <c r="E2" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="F2" s="11" t="s">
+      <c r="F2" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="G2" s="11" t="s">
+      <c r="G2" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="H2" s="11" t="s">
+      <c r="H2" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="J2" s="12" t="s">
+      <c r="I2" s="13"/>
+      <c r="J2" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="K2" s="10" t="s">
+      <c r="K2" s="5" t="s">
         <v>27</v>
       </c>
     </row>
@@ -2663,33 +2660,33 @@
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="13">
+      <c r="B3" s="6">
         <v>8</v>
       </c>
-      <c r="C3" s="13">
+      <c r="C3" s="6">
         <v>6</v>
       </c>
-      <c r="D3" s="13">
+      <c r="D3" s="6">
         <v>3</v>
       </c>
-      <c r="E3" s="13">
-        <v>14</v>
-      </c>
-      <c r="F3" s="13">
-        <v>6</v>
-      </c>
-      <c r="G3" s="13">
+      <c r="E3" s="6">
+        <v>10</v>
+      </c>
+      <c r="F3" s="6">
         <v>7</v>
       </c>
-      <c r="H3" s="13">
+      <c r="G3" s="6">
+        <v>7</v>
+      </c>
+      <c r="H3" s="6">
         <v>4</v>
       </c>
-      <c r="I3" s="13"/>
-      <c r="J3" s="13">
+      <c r="I3" s="6"/>
+      <c r="J3" s="6">
         <f>SUM(C3:H3)</f>
-        <v>40</v>
-      </c>
-      <c r="K3" s="7">
+        <v>37</v>
+      </c>
+      <c r="K3" s="6">
         <f>RANK(J3,$J$3:$J$18,1)</f>
         <v>5</v>
       </c>
@@ -2698,33 +2695,33 @@
       <c r="A4" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="13">
+      <c r="B4" s="6">
         <v>1</v>
       </c>
-      <c r="C4" s="13">
+      <c r="C4" s="6">
         <v>5</v>
       </c>
-      <c r="D4" s="13">
+      <c r="D4" s="6">
         <v>4</v>
       </c>
-      <c r="E4" s="13">
+      <c r="E4" s="6">
+        <v>4</v>
+      </c>
+      <c r="F4" s="6">
         <v>3</v>
       </c>
-      <c r="F4" s="13">
+      <c r="G4" s="6">
         <v>3</v>
       </c>
-      <c r="G4" s="13">
-        <v>3</v>
-      </c>
-      <c r="H4" s="13">
+      <c r="H4" s="6">
         <v>2</v>
       </c>
-      <c r="I4" s="13"/>
-      <c r="J4" s="13">
+      <c r="I4" s="6"/>
+      <c r="J4" s="6">
         <f t="shared" ref="J4:J18" si="0">SUM(C4:H4)</f>
-        <v>20</v>
-      </c>
-      <c r="K4" s="7">
+        <v>21</v>
+      </c>
+      <c r="K4" s="6">
         <f t="shared" ref="K4:K18" si="1">RANK(J4,$J$3:$J$18,1)</f>
         <v>2</v>
       </c>
@@ -2733,33 +2730,33 @@
       <c r="A5" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="13">
+      <c r="B5" s="6">
+        <v>16</v>
+      </c>
+      <c r="C5" s="6">
+        <v>12</v>
+      </c>
+      <c r="D5" s="6">
+        <v>16</v>
+      </c>
+      <c r="E5" s="6">
+        <v>11</v>
+      </c>
+      <c r="F5" s="6">
+        <v>16</v>
+      </c>
+      <c r="G5" s="6">
         <v>14</v>
       </c>
-      <c r="C5" s="13">
-        <v>12</v>
-      </c>
-      <c r="D5" s="13">
-        <v>15</v>
-      </c>
-      <c r="E5" s="13">
-        <v>11</v>
-      </c>
-      <c r="F5" s="13">
-        <v>16</v>
-      </c>
-      <c r="G5" s="13">
-        <v>15</v>
-      </c>
-      <c r="H5" s="13">
+      <c r="H5" s="6">
         <v>14</v>
       </c>
-      <c r="I5" s="13"/>
-      <c r="J5" s="13">
+      <c r="I5" s="6"/>
+      <c r="J5" s="6">
         <f t="shared" si="0"/>
         <v>83</v>
       </c>
-      <c r="K5" s="7">
+      <c r="K5" s="6">
         <f t="shared" si="1"/>
         <v>16</v>
       </c>
@@ -2768,68 +2765,68 @@
       <c r="A6" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B6" s="13">
-        <v>7</v>
-      </c>
-      <c r="C6" s="13">
+      <c r="B6" s="6">
+        <v>6</v>
+      </c>
+      <c r="C6" s="6">
         <v>16</v>
       </c>
-      <c r="D6" s="13">
+      <c r="D6" s="6">
         <v>8</v>
       </c>
-      <c r="E6" s="13">
-        <v>13</v>
-      </c>
-      <c r="F6" s="13">
-        <v>11</v>
-      </c>
-      <c r="G6" s="13">
+      <c r="E6" s="6">
+        <v>14</v>
+      </c>
+      <c r="F6" s="6">
+        <v>10</v>
+      </c>
+      <c r="G6" s="6">
         <v>8</v>
       </c>
-      <c r="H6" s="13">
+      <c r="H6" s="6">
         <v>6</v>
       </c>
-      <c r="I6" s="13"/>
-      <c r="J6" s="13">
+      <c r="I6" s="6"/>
+      <c r="J6" s="6">
         <f t="shared" si="0"/>
         <v>62</v>
       </c>
-      <c r="K6" s="7">
+      <c r="K6" s="6">
         <f t="shared" si="1"/>
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B7" s="13">
+      <c r="B7" s="6">
         <v>3</v>
       </c>
-      <c r="C7" s="13">
+      <c r="C7" s="6">
         <v>4</v>
       </c>
-      <c r="D7" s="13">
+      <c r="D7" s="6">
         <v>1</v>
       </c>
-      <c r="E7" s="13">
+      <c r="E7" s="6">
         <v>2</v>
       </c>
-      <c r="F7" s="13">
+      <c r="F7" s="6">
         <v>2</v>
       </c>
-      <c r="G7" s="13">
+      <c r="G7" s="6">
         <v>9</v>
       </c>
-      <c r="H7" s="13">
+      <c r="H7" s="6">
         <v>5</v>
       </c>
-      <c r="I7" s="13"/>
-      <c r="J7" s="13">
+      <c r="I7" s="6"/>
+      <c r="J7" s="6">
         <f t="shared" si="0"/>
         <v>23</v>
       </c>
-      <c r="K7" s="7">
+      <c r="K7" s="6">
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
@@ -2838,68 +2835,68 @@
       <c r="A8" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B8" s="13">
+      <c r="B8" s="6">
         <v>9</v>
       </c>
-      <c r="C8" s="13">
+      <c r="C8" s="6">
         <v>1</v>
       </c>
-      <c r="D8" s="13">
-        <v>14</v>
-      </c>
-      <c r="E8" s="13">
+      <c r="D8" s="6">
+        <v>15</v>
+      </c>
+      <c r="E8" s="6">
         <v>9</v>
       </c>
-      <c r="F8" s="13">
+      <c r="F8" s="6">
         <v>8</v>
       </c>
-      <c r="G8" s="13">
-        <v>13</v>
-      </c>
-      <c r="H8" s="13">
-        <v>9</v>
-      </c>
-      <c r="I8" s="13"/>
-      <c r="J8" s="13">
+      <c r="G8" s="6">
+        <v>15</v>
+      </c>
+      <c r="H8" s="6">
+        <v>10</v>
+      </c>
+      <c r="I8" s="6"/>
+      <c r="J8" s="6">
         <f t="shared" si="0"/>
-        <v>54</v>
-      </c>
-      <c r="K8" s="7">
+        <v>58</v>
+      </c>
+      <c r="K8" s="6">
         <f t="shared" si="1"/>
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B9" s="13">
+      <c r="B9" s="6">
         <v>13</v>
       </c>
-      <c r="C9" s="13">
+      <c r="C9" s="6">
         <v>9</v>
       </c>
-      <c r="D9" s="13">
+      <c r="D9" s="6">
         <v>9</v>
       </c>
-      <c r="E9" s="13">
+      <c r="E9" s="6">
         <v>12</v>
       </c>
-      <c r="F9" s="13">
+      <c r="F9" s="6">
         <v>9</v>
       </c>
-      <c r="G9" s="13">
+      <c r="G9" s="6">
         <v>11</v>
       </c>
-      <c r="H9" s="13">
+      <c r="H9" s="6">
         <v>16</v>
       </c>
-      <c r="I9" s="13"/>
-      <c r="J9" s="13">
+      <c r="I9" s="6"/>
+      <c r="J9" s="6">
         <f t="shared" si="0"/>
         <v>66</v>
       </c>
-      <c r="K9" s="7">
+      <c r="K9" s="6">
         <f t="shared" si="1"/>
         <v>13</v>
       </c>
@@ -2908,33 +2905,33 @@
       <c r="A10" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B10" s="13">
+      <c r="B10" s="6">
+        <v>14</v>
+      </c>
+      <c r="C10" s="6">
+        <v>11</v>
+      </c>
+      <c r="D10" s="6">
+        <v>10</v>
+      </c>
+      <c r="E10" s="6">
         <v>15</v>
       </c>
-      <c r="C10" s="13">
-        <v>11</v>
-      </c>
-      <c r="D10" s="13">
-        <v>10</v>
-      </c>
-      <c r="E10" s="13">
+      <c r="F10" s="6">
+        <v>14</v>
+      </c>
+      <c r="G10" s="6">
+        <v>12</v>
+      </c>
+      <c r="H10" s="6">
         <v>15</v>
       </c>
-      <c r="F10" s="13">
-        <v>15</v>
-      </c>
-      <c r="G10" s="13">
-        <v>14</v>
-      </c>
-      <c r="H10" s="13">
-        <v>15</v>
-      </c>
-      <c r="I10" s="13"/>
-      <c r="J10" s="13">
+      <c r="I10" s="6"/>
+      <c r="J10" s="6">
         <f t="shared" si="0"/>
-        <v>80</v>
-      </c>
-      <c r="K10" s="7">
+        <v>77</v>
+      </c>
+      <c r="K10" s="6">
         <f t="shared" si="1"/>
         <v>15</v>
       </c>
@@ -2943,68 +2940,68 @@
       <c r="A11" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B11" s="13">
+      <c r="B11" s="6">
         <v>4</v>
       </c>
-      <c r="C11" s="13">
-        <v>14</v>
-      </c>
-      <c r="D11" s="13">
+      <c r="C11" s="6">
+        <v>15</v>
+      </c>
+      <c r="D11" s="6">
         <v>13</v>
       </c>
-      <c r="E11" s="13">
-        <v>10</v>
-      </c>
-      <c r="F11" s="13">
-        <v>10</v>
-      </c>
-      <c r="G11" s="13">
+      <c r="E11" s="6">
+        <v>13</v>
+      </c>
+      <c r="F11" s="6">
+        <v>12</v>
+      </c>
+      <c r="G11" s="6">
         <v>1</v>
       </c>
-      <c r="H11" s="13">
+      <c r="H11" s="6">
         <v>1</v>
       </c>
-      <c r="I11" s="13"/>
-      <c r="J11" s="13">
+      <c r="I11" s="6"/>
+      <c r="J11" s="6">
         <f t="shared" si="0"/>
-        <v>49</v>
-      </c>
-      <c r="K11" s="7">
+        <v>55</v>
+      </c>
+      <c r="K11" s="6">
         <f t="shared" si="1"/>
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="12" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B12" s="13">
+      <c r="B12" s="6">
         <v>2</v>
       </c>
-      <c r="C12" s="13">
+      <c r="C12" s="6">
         <v>2</v>
       </c>
-      <c r="D12" s="13">
+      <c r="D12" s="6">
         <v>2</v>
       </c>
-      <c r="E12" s="13">
+      <c r="E12" s="6">
         <v>1</v>
       </c>
-      <c r="F12" s="13">
+      <c r="F12" s="6">
         <v>4</v>
       </c>
-      <c r="G12" s="13">
+      <c r="G12" s="6">
         <v>2</v>
       </c>
-      <c r="H12" s="13">
+      <c r="H12" s="6">
         <v>3</v>
       </c>
-      <c r="I12" s="13"/>
-      <c r="J12" s="13">
+      <c r="I12" s="6"/>
+      <c r="J12" s="6">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="K12" s="7">
+      <c r="K12" s="6">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -3013,68 +3010,68 @@
       <c r="A13" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B13" s="13">
-        <v>16</v>
-      </c>
-      <c r="C13" s="13">
+      <c r="B13" s="6">
+        <v>15</v>
+      </c>
+      <c r="C13" s="6">
         <v>8</v>
       </c>
-      <c r="D13" s="13">
-        <v>16</v>
-      </c>
-      <c r="E13" s="13">
+      <c r="D13" s="6">
+        <v>14</v>
+      </c>
+      <c r="E13" s="6">
         <v>8</v>
       </c>
-      <c r="F13" s="13">
+      <c r="F13" s="6">
         <v>5</v>
       </c>
-      <c r="G13" s="13">
+      <c r="G13" s="6">
         <v>5</v>
       </c>
-      <c r="H13" s="13">
+      <c r="H13" s="6">
         <v>8</v>
       </c>
-      <c r="I13" s="13"/>
-      <c r="J13" s="13">
+      <c r="I13" s="6"/>
+      <c r="J13" s="6">
         <f t="shared" si="0"/>
-        <v>50</v>
-      </c>
-      <c r="K13" s="7">
+        <v>48</v>
+      </c>
+      <c r="K13" s="6">
         <f t="shared" si="1"/>
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="14" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B14" s="13">
+      <c r="B14" s="6">
         <v>5</v>
       </c>
-      <c r="C14" s="13">
+      <c r="C14" s="6">
         <v>3</v>
       </c>
-      <c r="D14" s="13">
+      <c r="D14" s="6">
         <v>5</v>
       </c>
-      <c r="E14" s="13">
+      <c r="E14" s="6">
         <v>5</v>
       </c>
-      <c r="F14" s="13">
+      <c r="F14" s="6">
         <v>1</v>
       </c>
-      <c r="G14" s="13">
+      <c r="G14" s="6">
         <v>6</v>
       </c>
-      <c r="H14" s="13">
+      <c r="H14" s="6">
         <v>13</v>
       </c>
-      <c r="I14" s="13"/>
-      <c r="J14" s="13">
+      <c r="I14" s="6"/>
+      <c r="J14" s="6">
         <f t="shared" si="0"/>
         <v>33</v>
       </c>
-      <c r="K14" s="7">
+      <c r="K14" s="6">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
@@ -3083,33 +3080,33 @@
       <c r="A15" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B15" s="13">
+      <c r="B15" s="6">
         <v>10</v>
       </c>
-      <c r="C15" s="13">
+      <c r="C15" s="6">
         <v>7</v>
       </c>
-      <c r="D15" s="13">
+      <c r="D15" s="6">
         <v>6</v>
       </c>
-      <c r="E15" s="13">
+      <c r="E15" s="6">
         <v>7</v>
       </c>
-      <c r="F15" s="13">
-        <v>7</v>
-      </c>
-      <c r="G15" s="13">
+      <c r="F15" s="6">
+        <v>6</v>
+      </c>
+      <c r="G15" s="6">
         <v>10</v>
       </c>
-      <c r="H15" s="13">
-        <v>12</v>
-      </c>
-      <c r="I15" s="13"/>
-      <c r="J15" s="13">
+      <c r="H15" s="6">
+        <v>11</v>
+      </c>
+      <c r="I15" s="6"/>
+      <c r="J15" s="6">
         <f t="shared" si="0"/>
-        <v>49</v>
-      </c>
-      <c r="K15" s="7">
+        <v>47</v>
+      </c>
+      <c r="K15" s="6">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
@@ -3118,68 +3115,68 @@
       <c r="A16" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B16" s="13">
+      <c r="B16" s="6">
+        <v>7</v>
+      </c>
+      <c r="C16" s="6">
+        <v>10</v>
+      </c>
+      <c r="D16" s="6">
+        <v>12</v>
+      </c>
+      <c r="E16" s="6">
         <v>6</v>
       </c>
-      <c r="C16" s="13">
-        <v>10</v>
-      </c>
-      <c r="D16" s="13">
+      <c r="F16" s="6">
+        <v>13</v>
+      </c>
+      <c r="G16" s="6">
+        <v>4</v>
+      </c>
+      <c r="H16" s="6">
         <v>12</v>
       </c>
-      <c r="E16" s="13">
-        <v>6</v>
-      </c>
-      <c r="F16" s="13">
-        <v>12</v>
-      </c>
-      <c r="G16" s="13">
-        <v>4</v>
-      </c>
-      <c r="H16" s="13">
-        <v>11</v>
-      </c>
-      <c r="I16" s="13"/>
-      <c r="J16" s="13">
+      <c r="I16" s="6"/>
+      <c r="J16" s="6">
         <f t="shared" si="0"/>
-        <v>55</v>
-      </c>
-      <c r="K16" s="7">
+        <v>57</v>
+      </c>
+      <c r="K16" s="6">
         <f t="shared" si="1"/>
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B17" s="13">
+      <c r="B17" s="6">
         <v>12</v>
       </c>
-      <c r="C17" s="13">
+      <c r="C17" s="6">
+        <v>13</v>
+      </c>
+      <c r="D17" s="6">
+        <v>7</v>
+      </c>
+      <c r="E17" s="6">
+        <v>3</v>
+      </c>
+      <c r="F17" s="6">
         <v>15</v>
       </c>
-      <c r="D17" s="13">
-        <v>7</v>
-      </c>
-      <c r="E17" s="13">
-        <v>4</v>
-      </c>
-      <c r="F17" s="13">
-        <v>14</v>
-      </c>
-      <c r="G17" s="13">
-        <v>12</v>
-      </c>
-      <c r="H17" s="13">
-        <v>10</v>
-      </c>
-      <c r="I17" s="13"/>
-      <c r="J17" s="13">
+      <c r="G17" s="6">
+        <v>13</v>
+      </c>
+      <c r="H17" s="6">
+        <v>9</v>
+      </c>
+      <c r="I17" s="6"/>
+      <c r="J17" s="6">
         <f t="shared" si="0"/>
-        <v>62</v>
-      </c>
-      <c r="K17" s="7">
+        <v>60</v>
+      </c>
+      <c r="K17" s="6">
         <f t="shared" si="1"/>
         <v>11</v>
       </c>
@@ -3188,68 +3185,71 @@
       <c r="A18" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B18" s="13">
+      <c r="B18" s="6">
         <v>11</v>
       </c>
-      <c r="C18" s="13">
-        <v>13</v>
-      </c>
-      <c r="D18" s="13">
+      <c r="C18" s="6">
+        <v>14</v>
+      </c>
+      <c r="D18" s="6">
         <v>11</v>
       </c>
-      <c r="E18" s="13">
+      <c r="E18" s="6">
         <v>16</v>
       </c>
-      <c r="F18" s="13">
-        <v>13</v>
-      </c>
-      <c r="G18" s="13">
+      <c r="F18" s="6">
+        <v>11</v>
+      </c>
+      <c r="G18" s="6">
         <v>16</v>
       </c>
-      <c r="H18" s="13">
+      <c r="H18" s="6">
         <v>7</v>
       </c>
-      <c r="I18" s="13"/>
-      <c r="J18" s="13">
+      <c r="I18" s="6"/>
+      <c r="J18" s="6">
         <f t="shared" si="0"/>
-        <v>76</v>
-      </c>
-      <c r="K18" s="7">
+        <v>75</v>
+      </c>
+      <c r="K18" s="6">
         <f t="shared" si="1"/>
         <v>14</v>
       </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="K19" s="2"/>
     </row>
     <row r="20" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B20" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C20" s="14">
+      <c r="C20" s="7">
         <f t="shared" ref="C20:H20" si="2">CORREL($B$3:$B$18,C3:C18)</f>
-        <v>0.4</v>
-      </c>
-      <c r="D20" s="14">
+        <v>0.37058823529411766</v>
+      </c>
+      <c r="D20" s="7">
         <f t="shared" si="2"/>
-        <v>0.61176470588235299</v>
-      </c>
-      <c r="E20" s="14">
+        <v>0.62058823529411766</v>
+      </c>
+      <c r="E20" s="7">
         <f t="shared" si="2"/>
-        <v>0.5794117647058824</v>
-      </c>
-      <c r="F20" s="14">
+        <v>0.4823529411764706</v>
+      </c>
+      <c r="F20" s="7">
         <f t="shared" si="2"/>
-        <v>0.59411764705882353</v>
-      </c>
-      <c r="G20" s="14">
+        <v>0.58235294117647063</v>
+      </c>
+      <c r="G20" s="7">
         <f t="shared" si="2"/>
-        <v>0.6705882352941176</v>
-      </c>
-      <c r="H20" s="14">
+        <v>0.65</v>
+      </c>
+      <c r="H20" s="7">
         <f t="shared" si="2"/>
-        <v>0.67941176470588238</v>
-      </c>
-      <c r="K20" s="14">
+        <v>0.69117647058823528</v>
+      </c>
+      <c r="K20" s="7">
         <f t="shared" ref="K20" si="3">CORREL($B$3:$B$18,K3:K18)</f>
-        <v>0.79085644217822637</v>
+        <v>0.76470588235294112</v>
       </c>
     </row>
   </sheetData>
@@ -3259,7 +3259,7 @@
   <mergeCells count="1">
     <mergeCell ref="J1:K1"/>
   </mergeCells>
-  <phoneticPr fontId="3" type="noConversion"/>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -3268,514 +3268,518 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5A3B44DF-7868-4656-98E4-844C6F9ADDBB}">
   <dimension ref="A2:K20"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="9.140625" style="2"/>
+    <col min="2" max="2" width="19.140625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="2" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="5"/>
-      <c r="B2" s="4" t="s">
+      <c r="A2" s="10"/>
+      <c r="B2" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="C2" s="8" t="s">
+      <c r="C2" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="D2" s="8" t="s">
+      <c r="D2" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="E2" s="8" t="s">
+      <c r="E2" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="F2" s="8" t="s">
+      <c r="F2" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="G2" s="8" t="s">
+      <c r="G2" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="H2" s="8" t="s">
+      <c r="H2" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="I2" s="8" t="s">
+      <c r="I2" s="4" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="6">
+      <c r="A3" s="11">
         <v>1</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="7">
+      <c r="C3" s="6">
         <v>8</v>
       </c>
-      <c r="D3" s="7">
+      <c r="D3" s="6">
         <v>6</v>
       </c>
-      <c r="E3" s="7">
+      <c r="E3" s="6">
         <v>3</v>
       </c>
-      <c r="F3" s="7">
-        <v>14</v>
-      </c>
-      <c r="G3" s="7">
-        <v>6</v>
-      </c>
-      <c r="H3" s="7">
+      <c r="F3" s="6">
+        <v>10</v>
+      </c>
+      <c r="G3" s="6">
         <v>7</v>
       </c>
-      <c r="I3" s="7">
+      <c r="H3" s="6">
+        <v>7</v>
+      </c>
+      <c r="I3" s="6">
         <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="6">
+      <c r="A4" s="11">
         <v>2</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B4" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="7">
+      <c r="C4" s="6">
         <v>1</v>
       </c>
-      <c r="D4" s="7">
+      <c r="D4" s="6">
         <v>5</v>
       </c>
-      <c r="E4" s="7">
+      <c r="E4" s="6">
         <v>4</v>
       </c>
-      <c r="F4" s="7">
+      <c r="F4" s="6">
+        <v>4</v>
+      </c>
+      <c r="G4" s="6">
         <v>3</v>
       </c>
-      <c r="G4" s="7">
+      <c r="H4" s="6">
         <v>3</v>
       </c>
-      <c r="H4" s="7">
-        <v>3</v>
-      </c>
-      <c r="I4" s="7">
+      <c r="I4" s="6">
         <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="6">
+      <c r="A5" s="11">
         <v>3</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="B5" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="C5" s="7">
+      <c r="C5" s="6">
+        <v>16</v>
+      </c>
+      <c r="D5" s="6">
+        <v>12</v>
+      </c>
+      <c r="E5" s="6">
+        <v>16</v>
+      </c>
+      <c r="F5" s="6">
+        <v>11</v>
+      </c>
+      <c r="G5" s="6">
+        <v>16</v>
+      </c>
+      <c r="H5" s="6">
         <v>14</v>
       </c>
-      <c r="D5" s="7">
-        <v>12</v>
-      </c>
-      <c r="E5" s="7">
-        <v>15</v>
-      </c>
-      <c r="F5" s="7">
-        <v>11</v>
-      </c>
-      <c r="G5" s="7">
-        <v>16</v>
-      </c>
-      <c r="H5" s="7">
-        <v>15</v>
-      </c>
-      <c r="I5" s="7">
+      <c r="I5" s="6">
         <v>14</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="6">
+      <c r="A6" s="11">
         <v>4</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="B6" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="C6" s="7">
-        <v>7</v>
-      </c>
-      <c r="D6" s="7">
+      <c r="C6" s="6">
+        <v>6</v>
+      </c>
+      <c r="D6" s="6">
         <v>16</v>
       </c>
-      <c r="E6" s="7">
+      <c r="E6" s="6">
         <v>8</v>
       </c>
-      <c r="F6" s="7">
-        <v>13</v>
-      </c>
-      <c r="G6" s="7">
-        <v>11</v>
-      </c>
-      <c r="H6" s="7">
+      <c r="F6" s="6">
+        <v>14</v>
+      </c>
+      <c r="G6" s="6">
+        <v>10</v>
+      </c>
+      <c r="H6" s="6">
         <v>8</v>
       </c>
-      <c r="I6" s="7">
+      <c r="I6" s="6">
         <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="6">
+      <c r="A7" s="11">
         <v>5</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="B7" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="C7" s="7">
+      <c r="C7" s="6">
         <v>3</v>
       </c>
-      <c r="D7" s="7">
+      <c r="D7" s="6">
         <v>4</v>
       </c>
-      <c r="E7" s="7">
+      <c r="E7" s="6">
         <v>1</v>
       </c>
-      <c r="F7" s="7">
+      <c r="F7" s="6">
         <v>2</v>
       </c>
-      <c r="G7" s="7">
+      <c r="G7" s="6">
         <v>2</v>
       </c>
-      <c r="H7" s="7">
+      <c r="H7" s="6">
         <v>9</v>
       </c>
-      <c r="I7" s="7">
+      <c r="I7" s="6">
         <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="6">
+      <c r="A8" s="11">
         <v>6</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="B8" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="C8" s="7">
+      <c r="C8" s="6">
         <v>9</v>
       </c>
-      <c r="D8" s="7">
+      <c r="D8" s="6">
         <v>1</v>
       </c>
-      <c r="E8" s="7">
-        <v>14</v>
-      </c>
-      <c r="F8" s="7">
+      <c r="E8" s="6">
+        <v>15</v>
+      </c>
+      <c r="F8" s="6">
         <v>9</v>
       </c>
-      <c r="G8" s="7">
+      <c r="G8" s="6">
         <v>8</v>
       </c>
-      <c r="H8" s="7">
-        <v>13</v>
-      </c>
-      <c r="I8" s="7">
-        <v>9</v>
+      <c r="H8" s="6">
+        <v>15</v>
+      </c>
+      <c r="I8" s="6">
+        <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="6">
+      <c r="A9" s="11">
         <v>7</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="B9" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="C9" s="7">
+      <c r="C9" s="6">
         <v>13</v>
       </c>
-      <c r="D9" s="7">
+      <c r="D9" s="6">
         <v>9</v>
       </c>
-      <c r="E9" s="7">
+      <c r="E9" s="6">
         <v>9</v>
       </c>
-      <c r="F9" s="7">
+      <c r="F9" s="6">
         <v>12</v>
       </c>
-      <c r="G9" s="7">
+      <c r="G9" s="6">
         <v>9</v>
       </c>
-      <c r="H9" s="7">
+      <c r="H9" s="6">
         <v>11</v>
       </c>
-      <c r="I9" s="7">
+      <c r="I9" s="6">
         <v>16</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="6">
+      <c r="A10" s="11">
         <v>8</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="B10" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="C10" s="7">
+      <c r="C10" s="6">
+        <v>14</v>
+      </c>
+      <c r="D10" s="6">
+        <v>11</v>
+      </c>
+      <c r="E10" s="6">
+        <v>10</v>
+      </c>
+      <c r="F10" s="6">
         <v>15</v>
       </c>
-      <c r="D10" s="7">
-        <v>11</v>
-      </c>
-      <c r="E10" s="7">
-        <v>10</v>
-      </c>
-      <c r="F10" s="7">
-        <v>15</v>
-      </c>
-      <c r="G10" s="7">
-        <v>15</v>
-      </c>
-      <c r="H10" s="7">
+      <c r="G10" s="6">
         <v>14</v>
       </c>
-      <c r="I10" s="7">
+      <c r="H10" s="6">
+        <v>12</v>
+      </c>
+      <c r="I10" s="6">
         <v>15</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="6">
+      <c r="A11" s="11">
         <v>9</v>
       </c>
-      <c r="B11" s="1" t="s">
+      <c r="B11" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="C11" s="7">
+      <c r="C11" s="6">
         <v>4</v>
       </c>
-      <c r="D11" s="7">
-        <v>14</v>
-      </c>
-      <c r="E11" s="7">
+      <c r="D11" s="6">
+        <v>15</v>
+      </c>
+      <c r="E11" s="6">
         <v>13</v>
       </c>
-      <c r="F11" s="7">
-        <v>10</v>
-      </c>
-      <c r="G11" s="7">
-        <v>10</v>
-      </c>
-      <c r="H11" s="7">
+      <c r="F11" s="6">
+        <v>13</v>
+      </c>
+      <c r="G11" s="6">
+        <v>12</v>
+      </c>
+      <c r="H11" s="6">
         <v>1</v>
       </c>
-      <c r="I11" s="7">
+      <c r="I11" s="6">
         <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="6">
+      <c r="A12" s="11">
         <v>10</v>
       </c>
-      <c r="B12" s="1" t="s">
+      <c r="B12" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C12" s="7">
+      <c r="C12" s="6">
         <v>2</v>
       </c>
-      <c r="D12" s="7">
+      <c r="D12" s="6">
         <v>2</v>
       </c>
-      <c r="E12" s="7">
+      <c r="E12" s="6">
         <v>2</v>
       </c>
-      <c r="F12" s="7">
+      <c r="F12" s="6">
         <v>1</v>
       </c>
-      <c r="G12" s="7">
+      <c r="G12" s="6">
         <v>4</v>
       </c>
-      <c r="H12" s="7">
+      <c r="H12" s="6">
         <v>2</v>
       </c>
-      <c r="I12" s="7">
+      <c r="I12" s="6">
         <v>3</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="6">
+      <c r="A13" s="11">
         <v>11</v>
       </c>
-      <c r="B13" s="1" t="s">
+      <c r="B13" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C13" s="7">
-        <v>16</v>
-      </c>
-      <c r="D13" s="7">
+      <c r="C13" s="6">
+        <v>15</v>
+      </c>
+      <c r="D13" s="6">
         <v>8</v>
       </c>
-      <c r="E13" s="7">
-        <v>16</v>
-      </c>
-      <c r="F13" s="7">
+      <c r="E13" s="6">
+        <v>14</v>
+      </c>
+      <c r="F13" s="6">
         <v>8</v>
       </c>
-      <c r="G13" s="7">
+      <c r="G13" s="6">
         <v>5</v>
       </c>
-      <c r="H13" s="7">
+      <c r="H13" s="6">
         <v>5</v>
       </c>
-      <c r="I13" s="7">
+      <c r="I13" s="6">
         <v>8</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="6">
+      <c r="A14" s="11">
         <v>12</v>
       </c>
-      <c r="B14" s="1" t="s">
+      <c r="B14" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="C14" s="7">
+      <c r="C14" s="6">
         <v>5</v>
       </c>
-      <c r="D14" s="7">
+      <c r="D14" s="6">
         <v>3</v>
       </c>
-      <c r="E14" s="7">
+      <c r="E14" s="6">
         <v>5</v>
       </c>
-      <c r="F14" s="7">
+      <c r="F14" s="6">
         <v>5</v>
       </c>
-      <c r="G14" s="7">
+      <c r="G14" s="6">
         <v>1</v>
       </c>
-      <c r="H14" s="7">
+      <c r="H14" s="6">
         <v>6</v>
       </c>
-      <c r="I14" s="7">
+      <c r="I14" s="6">
         <v>13</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="6">
+      <c r="A15" s="11">
         <v>13</v>
       </c>
-      <c r="B15" s="1" t="s">
+      <c r="B15" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="C15" s="7">
+      <c r="C15" s="6">
         <v>10</v>
       </c>
-      <c r="D15" s="7">
+      <c r="D15" s="6">
         <v>7</v>
       </c>
-      <c r="E15" s="7">
+      <c r="E15" s="6">
         <v>6</v>
       </c>
-      <c r="F15" s="7">
+      <c r="F15" s="6">
         <v>7</v>
       </c>
-      <c r="G15" s="7">
-        <v>7</v>
-      </c>
-      <c r="H15" s="7">
+      <c r="G15" s="6">
+        <v>6</v>
+      </c>
+      <c r="H15" s="6">
         <v>10</v>
       </c>
-      <c r="I15" s="7">
-        <v>12</v>
+      <c r="I15" s="6">
+        <v>11</v>
       </c>
     </row>
     <row r="16" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="6">
+      <c r="A16" s="11">
         <v>14</v>
       </c>
-      <c r="B16" s="1" t="s">
+      <c r="B16" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="C16" s="7">
+      <c r="C16" s="6">
+        <v>7</v>
+      </c>
+      <c r="D16" s="6">
+        <v>10</v>
+      </c>
+      <c r="E16" s="6">
+        <v>12</v>
+      </c>
+      <c r="F16" s="6">
         <v>6</v>
       </c>
-      <c r="D16" s="7">
-        <v>10</v>
-      </c>
-      <c r="E16" s="7">
+      <c r="G16" s="6">
+        <v>13</v>
+      </c>
+      <c r="H16" s="6">
+        <v>4</v>
+      </c>
+      <c r="I16" s="6">
         <v>12</v>
-      </c>
-      <c r="F16" s="7">
-        <v>6</v>
-      </c>
-      <c r="G16" s="7">
-        <v>12</v>
-      </c>
-      <c r="H16" s="7">
-        <v>4</v>
-      </c>
-      <c r="I16" s="7">
-        <v>11</v>
       </c>
     </row>
     <row r="17" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="6">
+      <c r="A17" s="11">
         <v>15</v>
       </c>
-      <c r="B17" s="1" t="s">
+      <c r="B17" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="C17" s="7">
+      <c r="C17" s="6">
         <v>12</v>
       </c>
-      <c r="D17" s="7">
+      <c r="D17" s="6">
+        <v>13</v>
+      </c>
+      <c r="E17" s="6">
+        <v>7</v>
+      </c>
+      <c r="F17" s="6">
+        <v>3</v>
+      </c>
+      <c r="G17" s="6">
         <v>15</v>
       </c>
-      <c r="E17" s="7">
-        <v>7</v>
-      </c>
-      <c r="F17" s="7">
-        <v>4</v>
-      </c>
-      <c r="G17" s="7">
-        <v>14</v>
-      </c>
-      <c r="H17" s="7">
-        <v>12</v>
-      </c>
-      <c r="I17" s="7">
-        <v>10</v>
+      <c r="H17" s="6">
+        <v>13</v>
+      </c>
+      <c r="I17" s="6">
+        <v>9</v>
       </c>
     </row>
     <row r="18" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="6">
+      <c r="A18" s="11">
         <v>16</v>
       </c>
-      <c r="B18" s="1" t="s">
+      <c r="B18" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C18" s="7">
+      <c r="C18" s="6">
         <v>11</v>
       </c>
-      <c r="D18" s="7">
-        <v>13</v>
-      </c>
-      <c r="E18" s="7">
+      <c r="D18" s="6">
+        <v>14</v>
+      </c>
+      <c r="E18" s="6">
         <v>11</v>
       </c>
-      <c r="F18" s="7">
+      <c r="F18" s="6">
         <v>16</v>
       </c>
-      <c r="G18" s="7">
-        <v>13</v>
-      </c>
-      <c r="H18" s="7">
+      <c r="G18" s="6">
+        <v>11</v>
+      </c>
+      <c r="H18" s="6">
         <v>16</v>
       </c>
-      <c r="I18" s="7">
+      <c r="I18" s="6">
         <v>7</v>
       </c>
     </row>
     <row r="20" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B20" s="9"/>
-      <c r="C20" s="9"/>
-      <c r="D20" s="9"/>
-      <c r="E20" s="9"/>
-      <c r="F20" s="9"/>
-      <c r="G20" s="9"/>
-      <c r="H20" s="9"/>
-      <c r="I20" s="9"/>
+      <c r="B20" s="3"/>
+      <c r="C20" s="3"/>
+      <c r="D20" s="3"/>
+      <c r="E20" s="3"/>
+      <c r="F20" s="3"/>
+      <c r="G20" s="3"/>
+      <c r="H20" s="3"/>
+      <c r="I20" s="3"/>
       <c r="K20" t="e">
         <f t="shared" ref="K20" si="0">CORREL($B$3:$B$18,K3:K18)</f>
         <v>#DIV/0!</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="3" type="noConversion"/>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
